--- a/EnglishFootball/Planned Competition.xlsx
+++ b/EnglishFootball/Planned Competition.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1d7a30eff965ee96/Documents/GitHub/J-Ratings/EnglishFootball/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="80" documentId="11_F25DC773A252ABDACC1048F5D158512E5BDE58EA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1835D67E-90AA-4D70-AB7B-F7E45BC8DCEC}"/>
+  <xr:revisionPtr revIDLastSave="84" documentId="11_F25DC773A252ABDACC1048F5D158512E5BDE58EA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{238FC056-3825-43C8-A284-2CC6F7EE6EF7}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="114">
   <si>
     <t>Competition</t>
   </si>
@@ -159,12 +159,6 @@
     <t>Europe's main club competition</t>
   </si>
   <si>
-    <t>Europe's second European competition</t>
-  </si>
-  <si>
-    <t>Europe's third European competition</t>
-  </si>
-  <si>
     <t>Progress</t>
   </si>
   <si>
@@ -201,144 +195,96 @@
     <t>Primeira Liga</t>
   </si>
   <si>
-    <t>Liga Portugal 2</t>
-  </si>
-  <si>
     <t>Netherlands</t>
   </si>
   <si>
     <t>Eredivisie</t>
   </si>
   <si>
-    <t>Eerste Divisie</t>
-  </si>
-  <si>
     <t>Belgium</t>
   </si>
   <si>
     <t>Belgian Pro League</t>
   </si>
   <si>
-    <t>Challenger Pro League</t>
-  </si>
-  <si>
     <t>Scotland</t>
   </si>
   <si>
     <t>Scottish Premiership</t>
   </si>
   <si>
-    <t>Scottish Championship</t>
-  </si>
-  <si>
     <t>Turkey</t>
   </si>
   <si>
     <t>Süper Lig</t>
   </si>
   <si>
-    <t>TFF First League</t>
-  </si>
-  <si>
     <t>Austria</t>
   </si>
   <si>
     <t>Austrian Bundesliga</t>
   </si>
   <si>
-    <t>2. Liga</t>
-  </si>
-  <si>
     <t>Switzerland</t>
   </si>
   <si>
     <t>Swiss Super League</t>
   </si>
   <si>
-    <t>Challenge League</t>
-  </si>
-  <si>
     <t>Greece</t>
   </si>
   <si>
     <t>Super League Greece</t>
   </si>
   <si>
-    <t>Super League 2</t>
-  </si>
-  <si>
     <t>Czechia</t>
   </si>
   <si>
     <t>Czech First League</t>
   </si>
   <si>
-    <t>Czech National Football League</t>
-  </si>
-  <si>
     <t>Denmark</t>
   </si>
   <si>
     <t>Danish Superliga</t>
   </si>
   <si>
-    <t>Danish 1st Division</t>
-  </si>
-  <si>
     <t>Norway</t>
   </si>
   <si>
     <t>Eliteserien</t>
   </si>
   <si>
-    <t>Norwegian First Division</t>
-  </si>
-  <si>
     <t>Sweden</t>
   </si>
   <si>
     <t>Allsvenskan</t>
   </si>
   <si>
-    <t>Superettan</t>
-  </si>
-  <si>
     <t>Poland</t>
   </si>
   <si>
     <t>Ekstraklasa</t>
   </si>
   <si>
-    <t>I liga</t>
-  </si>
-  <si>
     <t>Croatia</t>
   </si>
   <si>
     <t>Croatian Football League</t>
   </si>
   <si>
-    <t>First Football League</t>
-  </si>
-  <si>
     <t>Serbia</t>
   </si>
   <si>
     <t>Serbian SuperLiga</t>
   </si>
   <si>
-    <t>Serbian First League</t>
-  </si>
-  <si>
     <t>Ukraine</t>
   </si>
   <si>
     <t>Ukrainian Premier League</t>
   </si>
   <si>
-    <t>Ukrainian First League</t>
-  </si>
-  <si>
     <t>Country</t>
   </si>
   <si>
@@ -360,64 +306,67 @@
     <t>England</t>
   </si>
   <si>
-    <t>Arsenal</t>
-  </si>
-  <si>
-    <t>Manchester City</t>
-  </si>
-  <si>
-    <t>Liverpool</t>
-  </si>
-  <si>
-    <t>Manchester United</t>
-  </si>
-  <si>
-    <t>Aston Villa</t>
-  </si>
-  <si>
-    <t>Bournemouth</t>
-  </si>
-  <si>
-    <t>Brighton &amp; Hove Albion</t>
-  </si>
-  <si>
-    <t>Brentford</t>
-  </si>
-  <si>
-    <t>Chelsea</t>
-  </si>
-  <si>
-    <t>Newcastle United</t>
-  </si>
-  <si>
-    <t>Fulham</t>
-  </si>
-  <si>
-    <t>Nottingham Forest</t>
-  </si>
-  <si>
-    <t>Everton</t>
-  </si>
-  <si>
-    <t>Leeds United</t>
-  </si>
-  <si>
-    <t>Crystal Palace</t>
-  </si>
-  <si>
-    <t>Tottenham Hotspur</t>
-  </si>
-  <si>
-    <t>West Ham United</t>
-  </si>
-  <si>
-    <t>Sunderland</t>
-  </si>
-  <si>
-    <t>Wolverhampton Wanderers</t>
-  </si>
-  <si>
-    <t>Burnley</t>
+    <t>Added to 2018/19</t>
+  </si>
+  <si>
+    <t>Europe's second club competition</t>
+  </si>
+  <si>
+    <t>Europe's third club competition</t>
+  </si>
+  <si>
+    <t>Added to 2021/22</t>
+  </si>
+  <si>
+    <t>Portugal division 1</t>
+  </si>
+  <si>
+    <t>Netherlands division 1</t>
+  </si>
+  <si>
+    <t>Belgium division 1</t>
+  </si>
+  <si>
+    <t>Scotland division 1</t>
+  </si>
+  <si>
+    <t>Turkey division 1</t>
+  </si>
+  <si>
+    <t>Austria division 1</t>
+  </si>
+  <si>
+    <t>Switzerland division 1</t>
+  </si>
+  <si>
+    <t>Greece division 1</t>
+  </si>
+  <si>
+    <t>Czechia division 1</t>
+  </si>
+  <si>
+    <t>Denmark division 1</t>
+  </si>
+  <si>
+    <t>Norway division 1</t>
+  </si>
+  <si>
+    <t>Sweden division 1</t>
+  </si>
+  <si>
+    <t>Poland division 1</t>
+  </si>
+  <si>
+    <t>Croatia division 1</t>
+  </si>
+  <si>
+    <t>Serbia division 1</t>
+  </si>
+  <si>
+    <t>Ukraine division 1</t>
+  </si>
+  <si>
+    <t>Added to 2023/24</t>
   </si>
 </sst>
 </file>
@@ -441,7 +390,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -451,12 +400,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF00B050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -479,7 +422,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -491,9 +434,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -514,10 +454,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -783,20 +719,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:J40"/>
+  <dimension ref="B2:E40"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="9.23046875" style="6"/>
-    <col min="2" max="2" width="10.921875" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.07421875" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="33.69140625" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.765625" style="6" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.23046875" style="6"/>
+    <col min="1" max="1" width="9.23046875" style="5"/>
+    <col min="2" max="2" width="10.921875" style="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.07421875" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="33.69140625" style="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.765625" style="5" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.23046875" style="5"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B2" s="2" t="s">
-        <v>104</v>
+        <v>86</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>0</v>
@@ -805,12 +741,12 @@
         <v>1</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.4">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="3" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B3" s="1" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>2</v>
@@ -818,13 +754,13 @@
       <c r="D3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="4" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="E3" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="4" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B4" s="1" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>4</v>
@@ -833,12 +769,12 @@
         <v>5</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.4">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B5" s="1" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>6</v>
@@ -847,12 +783,12 @@
         <v>7</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.4">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B6" s="1" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>8</v>
@@ -861,12 +797,12 @@
         <v>9</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.4">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B7" s="1" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>10</v>
@@ -874,13 +810,13 @@
       <c r="D7" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E7" s="4" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="E7" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B8" s="1" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>12</v>
@@ -888,13 +824,13 @@
       <c r="D8" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E8" s="5" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="E8" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="9" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B9" s="1" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>14</v>
@@ -902,13 +838,13 @@
       <c r="D9" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E9" s="5" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="E9" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B10" s="1" t="s">
-        <v>109</v>
+        <v>91</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>16</v>
@@ -917,12 +853,12 @@
         <v>17</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.4">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B11" s="1" t="s">
-        <v>109</v>
+        <v>91</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>18</v>
@@ -931,12 +867,12 @@
         <v>19</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.4">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B12" s="1" t="s">
-        <v>109</v>
+        <v>91</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>20</v>
@@ -944,13 +880,13 @@
       <c r="D12" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E12" s="5" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="E12" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="13" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B13" s="1" t="s">
-        <v>108</v>
+        <v>90</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>22</v>
@@ -959,12 +895,12 @@
         <v>23</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="14" spans="2:10" x14ac:dyDescent="0.4">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="14" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B14" s="1" t="s">
-        <v>108</v>
+        <v>90</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>24</v>
@@ -973,12 +909,12 @@
         <v>25</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.4">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="15" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B15" s="1" t="s">
-        <v>108</v>
+        <v>90</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>26</v>
@@ -986,13 +922,13 @@
       <c r="D15" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E15" s="5" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="E15" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="16" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B16" s="1" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>28</v>
@@ -1001,24 +937,12 @@
         <v>29</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="G16" s="6">
-        <v>2</v>
-      </c>
-      <c r="H16" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="I16" s="6">
-        <v>3059</v>
-      </c>
-      <c r="J16" s="6" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.4">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B17" s="1" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>30</v>
@@ -1027,24 +951,12 @@
         <v>31</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="G17" s="6">
-        <v>6</v>
-      </c>
-      <c r="H17" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="I17" s="6">
-        <v>3000</v>
-      </c>
-      <c r="J17" s="6" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.4">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="18" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B18" s="1" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>32</v>
@@ -1052,25 +964,13 @@
       <c r="D18" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="E18" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="G18" s="6">
-        <v>8</v>
-      </c>
-      <c r="H18" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="I18" s="6">
-        <v>2942</v>
-      </c>
-      <c r="J18" s="6" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="E18" s="3" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B19" s="1" t="s">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>34</v>
@@ -1079,24 +979,12 @@
         <v>35</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="G19" s="6">
-        <v>10</v>
-      </c>
-      <c r="H19" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="I19" s="6">
-        <v>2921</v>
-      </c>
-      <c r="J19" s="6" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.4">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="20" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B20" s="1" t="s">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>36</v>
@@ -1105,24 +993,12 @@
         <v>37</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="G20" s="6">
-        <v>12</v>
-      </c>
-      <c r="H20" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="I20" s="6">
-        <v>2913</v>
-      </c>
-      <c r="J20" s="6" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.4">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="21" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B21" s="1" t="s">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>38</v>
@@ -1130,25 +1006,13 @@
       <c r="D21" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="E21" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="G21" s="6">
-        <v>19</v>
-      </c>
-      <c r="H21" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="I21" s="6">
-        <v>2887</v>
-      </c>
-      <c r="J21" s="6" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="E21" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="22" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B22" s="1" t="s">
-        <v>105</v>
+        <v>87</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>40</v>
@@ -1157,427 +1021,259 @@
         <v>43</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="G22" s="6">
-        <v>28</v>
-      </c>
-      <c r="H22" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="I22" s="6">
-        <v>2856</v>
-      </c>
-      <c r="J22" s="6" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.4">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="23" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B23" s="1" t="s">
-        <v>105</v>
+        <v>87</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="E23" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="G23" s="6">
-        <v>31</v>
-      </c>
-      <c r="H23" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="I23" s="6">
-        <v>2846</v>
-      </c>
-      <c r="J23" s="6" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.4">
+        <v>94</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="24" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B24" s="1" t="s">
-        <v>105</v>
+        <v>87</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E24" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="25" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B25" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="26" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B26" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="27" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B27" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="28" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B28" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="29" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B29" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="30" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B30" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="E30" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="G24" s="6">
-        <v>32</v>
-      </c>
-      <c r="H24" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="I24" s="6">
-        <v>2846</v>
-      </c>
-      <c r="J24" s="6" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B25" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="C25" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="D25" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="E25" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="G25" s="6">
-        <v>33</v>
-      </c>
-      <c r="H25" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="I25" s="6">
-        <v>2838</v>
-      </c>
-      <c r="J25" s="6" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="26" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B26" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="C26" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="D26" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="E26" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="G26" s="6">
-        <v>37</v>
-      </c>
-      <c r="H26" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="I26" s="6">
-        <v>2828</v>
-      </c>
-      <c r="J26" s="6" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="27" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B27" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="C27" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="D27" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="E27" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="G27" s="6">
-        <v>39</v>
-      </c>
-      <c r="H27" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="I27" s="6">
-        <v>2821</v>
-      </c>
-      <c r="J27" s="6" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="28" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B28" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="C28" s="6" t="s">
+    </row>
+    <row r="31" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B31" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="D28" s="6" t="s">
+      <c r="C31" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="E28" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="G28" s="6">
-        <v>40</v>
-      </c>
-      <c r="H28" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="I28" s="6">
-        <v>2815</v>
-      </c>
-      <c r="J28" s="6" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="29" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B29" s="6" t="s">
+      <c r="D31" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="32" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B32" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="C29" s="6" t="s">
+      <c r="C32" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="D29" s="6" t="s">
+      <c r="D32" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="33" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B33" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="E29" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="G29" s="6">
-        <v>42</v>
-      </c>
-      <c r="H29" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="I29" s="6">
-        <v>2814</v>
-      </c>
-      <c r="J29" s="6" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="30" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B30" s="6" t="s">
+      <c r="C33" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="C30" s="6" t="s">
+      <c r="D33" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="34" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B34" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="D30" s="6" t="s">
+      <c r="C34" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="E30" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="G30" s="6">
-        <v>43</v>
-      </c>
-      <c r="H30" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="I30" s="6">
-        <v>2812</v>
-      </c>
-      <c r="J30" s="6" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="31" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B31" s="6" t="s">
+      <c r="D34" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="35" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B35" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="C31" s="6" t="s">
+      <c r="C35" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="D31" s="6" t="s">
+      <c r="D35" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="E35" s="4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="36" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B36" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="E31" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="G31" s="6">
-        <v>48</v>
-      </c>
-      <c r="H31" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="I31" s="6">
-        <v>2791</v>
-      </c>
-      <c r="J31" s="6" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="32" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B32" s="6" t="s">
+      <c r="C36" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="C32" s="6" t="s">
+      <c r="D36" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="E36" s="4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="37" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B37" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="D32" s="6" t="s">
+      <c r="C37" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="E32" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="G32" s="6">
-        <v>51</v>
-      </c>
-      <c r="H32" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="I32" s="6">
-        <v>2779</v>
-      </c>
-      <c r="J32" s="6" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="33" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B33" s="6" t="s">
+      <c r="D37" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="E37" s="4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="38" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B38" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="C33" s="6" t="s">
+      <c r="C38" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="D33" s="6" t="s">
+      <c r="D38" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="E38" s="4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="39" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B39" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="E33" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="G33" s="6">
-        <v>57</v>
-      </c>
-      <c r="H33" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="I33" s="6">
-        <v>2768</v>
-      </c>
-      <c r="J33" s="6" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="34" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B34" s="6" t="s">
+      <c r="C39" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="C34" s="6" t="s">
+      <c r="D39" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="E39" s="4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="40" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B40" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="D34" s="6" t="s">
+      <c r="C40" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="E34" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="G34" s="6">
-        <v>85</v>
-      </c>
-      <c r="H34" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="I34" s="6">
-        <v>2698</v>
-      </c>
-      <c r="J34" s="6" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="35" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B35" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="C35" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="D35" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="E35" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="G35" s="6">
-        <v>88</v>
-      </c>
-      <c r="H35" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="I35" s="6">
-        <v>2687</v>
-      </c>
-      <c r="J35" s="6" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="36" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B36" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="C36" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="D36" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="E36" s="5" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="37" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B37" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="C37" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="D37" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="E37" s="5" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="38" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B38" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="C38" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="D38" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="E38" s="5" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="39" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B39" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="C39" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="D39" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="E39" s="5" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="40" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B40" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="C40" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="D40" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="E40" s="5" t="s">
-        <v>51</v>
+      <c r="D40" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>113</v>
       </c>
     </row>
   </sheetData>
